--- a/혼다_models.xlsx
+++ b/혼다_models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'혼다 트랜스폰더 DB'!$A$1:$P$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'혼다 트랜스폰더 DB'!$A$1:$P$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P117"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2012(단종)</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -2512,22 +2512,22 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>어코드 (8세대)</t>
+          <t>어코드 (9세대)</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>2013(단종)</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -2537,35 +2537,35 @@
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7961)</t>
+          <t>ID47(NCF2952X)</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>72147-TA0-U11[리모컨키, 해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
           <t>HON66</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr"/>
-      <c r="L32" s="9" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>72147-T2A-Y01[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M32" s="9" t="inlineStr"/>
       <c r="N32" s="9" t="inlineStr">
         <is>
-          <t>이모빌라이저 ECU</t>
+          <t>스마트키 ECU</t>
         </is>
       </c>
       <c r="O32" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Accord 2008–2012 Hitag2 ID46 PCF7936·PCF7961 리모컨 키 35118-TA0-A04) — 북미형 313.8MHz(FCC KR55WK49308·MLBHLIK-1T)라 뺌, abkeys(순정 Accord 2007-2012 리모컨 일체형 키 72147-TA0-U11 433MHz HON66), 위키백과(2008 수입차 판매 1위)</t>
+          <t>transpondery(Honda Catalog Accord 2013–2017 Philips Hitag3 ID47 NCF2952X 스마트키 72147-T2A-A02·A22) — 북미형 313.8MHz(FCC ACJ932HK1210A)라 뺌, abkeys(Accord 2013-2016 스마트키 72147-T2A-Y01 433MHz), RPM9·다나와(9세대 2012.12 국내 출시)</t>
         </is>
       </c>
       <c r="P32" s="9" t="inlineStr"/>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="O33" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Accord 2013–2017 Philips Hitag3 ID47 NCF2952X 스마트키 72147-T2A-A02·A22) — 북미형 313.8MHz(FCC ACJ932HK1210A)라 뺌, abkeys(Accord 2013-2016 스마트키 72147-T2A-Y01 433MHz)</t>
+          <t>transpondery(Honda Catalog Accord 2013–2017 Philips Hitag3 ID47 NCF2952X 스마트키 72147-T2A-A02·A22) — 북미형 313.8MHz(FCC ACJ932HK1210A)라 뺌, abkeys(Accord 2013-2016 스마트키 72147-T2A-Y01 433MHz), RPM9·다나와(9세대 2012.12 국내 출시)</t>
         </is>
       </c>
       <c r="P33" s="9" t="inlineStr"/>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="O34" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Accord 2013–2017 Philips Hitag3 ID47 NCF2952X 스마트키 72147-T2A-A02·A22) — 북미형 313.8MHz(FCC ACJ932HK1210A)라 뺌, abkeys(Accord 2013-2016 스마트키 72147-T2A-Y01 433MHz)</t>
+          <t>transpondery(Honda Catalog Accord 2013–2017 Philips Hitag3 ID47 NCF2952X 스마트키 72147-T2A-A02·A22) — 북미형 313.8MHz(FCC ACJ932HK1210A)라 뺌, abkeys(Accord 2013-2016 스마트키 72147-T2A-Y01 433MHz), RPM9·다나와(9세대 2012.12 국내 출시)</t>
         </is>
       </c>
       <c r="P34" s="9" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="O35" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Accord 2013–2017 Philips Hitag3 ID47 NCF2952X 스마트키 72147-T2A-A02·A22) — 북미형 313.8MHz(FCC ACJ932HK1210A)라 뺌, abkeys(Accord 2013-2016 스마트키 72147-T2A-Y01 433MHz)</t>
+          <t>transpondery(Honda Catalog Accord 2013–2017 Philips Hitag3 ID47 NCF2952X 스마트키 72147-T2A-A02·A22) — 북미형 313.8MHz(FCC ACJ932HK1210A)라 뺌, abkeys(Accord 2013-2016 스마트키 72147-T2A-Y01 433MHz), RPM9·다나와(9세대 2012.12 국내 출시)</t>
         </is>
       </c>
       <c r="P35" s="9" t="inlineStr"/>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O109" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 목록(2018-현재)</t>
+          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 모터그래프·다나와(5세대 올 뉴 오딧세이 2017.10.23 국내 출시), 한국경제·토픽트리(혼다코리아 2026년 말 자동차 판매 종료 발표)</t>
         </is>
       </c>
       <c r="P109" s="9" t="inlineStr"/>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="O110" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 목록(2018-현재)</t>
+          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 모터그래프·다나와(5세대 올 뉴 오딧세이 2017.10.23 국내 출시), 한국경제·토픽트리(혼다코리아 2026년 말 자동차 판매 종료 발표)</t>
         </is>
       </c>
       <c r="P110" s="9" t="inlineStr"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="O111" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 목록(2018-현재)</t>
+          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 모터그래프·다나와(5세대 올 뉴 오딧세이 2017.10.23 국내 출시), 한국경제·토픽트리(혼다코리아 2026년 말 자동차 판매 종료 발표)</t>
         </is>
       </c>
       <c r="P111" s="9" t="inlineStr"/>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="O112" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 목록(2018-현재)</t>
+          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 모터그래프·다나와(5세대 올 뉴 오딧세이 2017.10.23 국내 출시), 한국경제·토픽트리(혼다코리아 2026년 말 자동차 판매 종료 발표)</t>
         </is>
       </c>
       <c r="P112" s="9" t="inlineStr"/>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="O113" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 목록(2018-현재)</t>
+          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 모터그래프·다나와(5세대 올 뉴 오딧세이 2017.10.23 국내 출시), 한국경제·토픽트리(혼다코리아 2026년 말 자동차 판매 종료 발표)</t>
         </is>
       </c>
       <c r="P113" s="9" t="inlineStr"/>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="O114" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 목록(2018-현재)</t>
+          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 모터그래프·다나와(5세대 올 뉴 오딧세이 2017.10.23 국내 출시), 한국경제·토픽트리(혼다코리아 2026년 말 자동차 판매 종료 발표)</t>
         </is>
       </c>
       <c r="P114" s="9" t="inlineStr"/>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="O115" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 목록(2018-현재)</t>
+          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 모터그래프·다나와(5세대 올 뉴 오딧세이 2017.10.23 국내 출시), 한국경제·토픽트리(혼다코리아 2026년 말 자동차 판매 종료 발표)</t>
         </is>
       </c>
       <c r="P115" s="9" t="inlineStr"/>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="O116" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 목록(2018-현재)</t>
+          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 모터그래프·다나와(5세대 올 뉴 오딧세이 2017.10.23 국내 출시), 한국경제·토픽트리(혼다코리아 2026년 말 자동차 판매 종료 발표)</t>
         </is>
       </c>
       <c r="P116" s="9" t="inlineStr"/>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -8075,13 +8075,79 @@
       </c>
       <c r="O117" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 목록(2018-현재)</t>
+          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 모터그래프·다나와(5세대 올 뉴 오딧세이 2017.10.23 국내 출시), 한국경제·토픽트리(혼다코리아 2026년 말 자동차 판매 종료 발표)</t>
         </is>
       </c>
       <c r="P117" s="9" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>혼다</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr">
+        <is>
+          <t>오딧세이 (북미형, 5세대)</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>ID47(NCF2952X)</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I118" s="9" t="inlineStr"/>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>HON66</t>
+        </is>
+      </c>
+      <c r="K118" s="9" t="inlineStr"/>
+      <c r="L118" s="9" t="inlineStr">
+        <is>
+          <t>72147-THR-A11[해외 공용 품번], 72147-THR-A21[해외 공용 품번], 72147-THR-A31[해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="M118" s="9" t="inlineStr"/>
+      <c r="N118" s="9" t="inlineStr">
+        <is>
+          <t>스마트키 ECU</t>
+        </is>
+      </c>
+      <c r="O118" s="9" t="inlineStr">
+        <is>
+          <t>transpondery(Honda Catalog Odyssey 2018–2026 Hitag3 ID47 NCF2952X 스마트키 72147-THR-A11·A21·A31 FCC KR5V2X(433MHz), HON66 비상키), 모터그래프·다나와(5세대 올 뉴 오딧세이 2017.10.23 국내 출시), 한국경제·토픽트리(혼다코리아 2026년 말 자동차 판매 종료 발표)</t>
+        </is>
+      </c>
+      <c r="P118" s="9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P117"/>
+  <autoFilter ref="A1:P118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8092,7 +8158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -8239,140 +8305,154 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>- CR-V 2세대 후기형: 2004 혼다코리아 진출과 함께 수입 → 2004~2006 / CR-V 5세대: 2017.3.30~2022(6세대 2023.4.11) / 크로스투어: 2012.12 출시 → 2012~2015 / 오딧세이 4세대: 2012.11.30 국내 출시 → 2012~2017.</t>
+          <t>- 어코드 8세대: 2008~2012, 9세대: 2012.12 국내 출시 → 2012~2017 / 오딧세이 5세대: 2017.10.23 국내 출시 → 2017~.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr"/>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>- 혼다코리아는 2026년 말 자동차 판매 종료를 발표(2026.4) — 현재 판매 모델은 2026년까지 기록.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>※ 출처</t>
+          <t>- CR-V 2세대 후기형: 2004 혼다코리아 진출과 함께 수입 → 2004~2006 / CR-V 5세대: 2017.3.30~2022(6세대 2023.4.11) / 크로스투어: 2012.12 출시 → 2012~2015 / 오딧세이 4세대: 2012.11.30 국내 출시 → 2012~2017.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>- transpondery.com Honda Transponder Catalog(모델·생산기간별 칩·OEM 키·FCC ID·키 블레이드), abkeys.com 순정 키(품번별 주파수·적용 연식), 한국어 위키백과·나무위키·다나와, 국내 출시 기사(이데일리·한국일보·이투데이·아시아경제 등).</t>
-        </is>
-      </c>
+      <c r="A26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
+          <t>※ 출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>- transpondery.com Honda Transponder Catalog(모델·생산기간별 칩·OEM 키·FCC ID·키 블레이드), abkeys.com 순정 키(품번별 주파수·적용 연식), 한국어 위키백과·나무위키·다나와, 국내 출시 기사(이데일리·한국일보·이투데이·아시아경제 등).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
           <t>- 연식별 근거는 research/import5/yearly_honda.md에 있습니다.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
-        </is>
-      </c>
+      <c r="A30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
+          <t>※ 표기 규칙 (칩코드·부품번호·키웨이·이모빌라이저 칸 공통)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
+          <t>- 한 칸에 값이 여러 개면 ', '(쉼표)로만 구분합니다. '/', '·', '또는'은 쓰지 않고, 줄임(예: 4F0837220M/T, 5WK49145~49147)도 모두 풀어서 따로 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
+          <t>- ( ) 안에는 부품번호만 적습니다. 칩코드 'ID49(PCF7953)' = ID49 칩, 칩 부품번호 PCF7953. 이모빌라이저 'SKM(87570-36010)' = SKM 모듈, 품번 87570-36010. 칩 부품번호를 모르면 'ID46'처럼 ID만 적었습니다.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+          <t>- [ ] 안에는 그 값이 적용되는 조건을 적습니다(키 종류·버튼 수·옵션·생산 시기·차종 코드). 예: ID46(PCF7936)[폴딩키], ID46(PCF7952A)[스마트키] → 폴딩키는 PCF7936, 스마트키는 PCF7952A.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
+          <t>- [추정] = 추정값, [일부 자료] = 일부 자료에만 나오는 값, [자료 상충] = 자료마다 달라 둘 중 무엇인지 미확정, [해외 공용 품번] = 해외 공용 품번(국내 순정 품번 미확인).</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>- 부품번호 칸에는 부품번호만 적습니다. 'FCC ' = 미국 FCC 인증번호(키 모델 식별용), 'KC ' = 한국 전파인증번호. 순정(제조사) 부품번호만 적고 애프터마켓 호환품 번호는 넣지 않았습니다. 설명·판매처·주파수(모두 국내 433/434MHz)는 적지 않았고, 부품번호가 없으면 공란입니다.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>※ 칩 ID 코드 뜻</t>
+          <t>- Hitag2·Hitag Pro·Megamos·DST80 같은 칩 방식 이름은 ID 코드와 같은 뜻이라 칸에 따로 적지 않았습니다(아래 표).</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
-        </is>
-      </c>
+      <c r="A38" s="11" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
+          <t>※ 칩 ID 코드 뜻</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
+          <t>- ID13: Megamos 13(고정 코드)  |  ID44: Philips Crypto(PCF7935, BMW EWS 구형)  |  ID48: Megamos Crypto</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
+          <t>- ID46: Philips Hitag2 계열(PCF7936·PCF7941·PCF7945·PCF7952 등). [Extended] = Hitag2 Extended, [Circle Plus] = GM Circle Plus</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
+          <t>- ID47: NXP Hitag3(NCF2951·NCF2952·NCF2971·PCF7938 등)  |  ID49: NXP Hitag Pro(PCF7953P·NCF2951·NCF295X 등)  |  ID4A: NXP Hitag AES(NCF29A1M·PCF7953M·PCF7961M 등)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
+          <t>- ID60: Texas 4D60(40bit)  |  4D60x80: Texas 4D60 80bit(DST80 계열)  |  ID70: Texas 4D70  |  ID6E-MA: Texas DST80(현대·기아 표기)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>- ID6A·ID8A: Texas Crypto AES(DST-AES)  |  ID75: Texas AES(판매처 표기)  |  ID88: Megamos AES(VW·아우디 MQB)  |  ID8E: 아우디 8E Crypto(Sokymat 8E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>- FBS3·FBS4: 벤츠 NEC 프로세서 키(ID 칩이 아님)  |  MLB 전용 칩·MLB evo 전용 칩: 아우디 MLB 플랫폼 전용 키 칩</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>- 확인 불가 = 자료로 확인하지 못함  |  해당 없음 = 이모빌라이저 미적용</t>
         </is>
